--- a/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
+++ b/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="73">
   <si>
     <t>Record</t>
   </si>
@@ -39,187 +39,202 @@
     <t>Team Rodriguez</t>
   </si>
   <si>
+    <t>Michael's Monstrous Team</t>
+  </si>
+  <si>
     <t>Dirty Tone and  The Boys</t>
   </si>
   <si>
+    <t xml:space="preserve">Peter Pan + the Lost Boys </t>
+  </si>
+  <si>
+    <t>Crazy Kat</t>
+  </si>
+  <si>
     <t>Febreze Brothers</t>
   </si>
   <si>
-    <t>Crazy Kat</t>
-  </si>
-  <si>
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>Michael's Monstrous Team</t>
+    <t>The Upside Down</t>
   </si>
   <si>
     <t>Wu-Tangs Killabeez</t>
   </si>
   <si>
-    <t xml:space="preserve">Peter Pan + the Lost Boys </t>
-  </si>
-  <si>
-    <t>The Upside Down</t>
+    <t xml:space="preserve">The Price is Wrong Bob </t>
   </si>
   <si>
     <t>Toon Squad</t>
   </si>
   <si>
-    <t xml:space="preserve">The Price is Wrong Bob </t>
-  </si>
-  <si>
     <t>Crunchwrap Crew</t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>96.3%</t>
-  </si>
-  <si>
-    <t>92.8%</t>
-  </si>
-  <si>
-    <t>89.0%</t>
-  </si>
-  <si>
-    <t>70.6%</t>
-  </si>
-  <si>
-    <t>63.8%</t>
-  </si>
-  <si>
-    <t>40.0%</t>
-  </si>
-  <si>
-    <t>32.4%</t>
-  </si>
-  <si>
-    <t>11.0%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>98.7%</t>
+  </si>
+  <si>
+    <t>96.7%</t>
+  </si>
+  <si>
+    <t>90.5%</t>
+  </si>
+  <si>
+    <t>90.4%</t>
+  </si>
+  <si>
+    <t>68.7%</t>
+  </si>
+  <si>
+    <t>27.8%</t>
+  </si>
+  <si>
+    <t>8.0%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>7.1%</t>
+  </si>
+  <si>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-7592</t>
+  </si>
+  <si>
+    <t>-2930</t>
+  </si>
+  <si>
+    <t>-953</t>
+  </si>
+  <si>
+    <t>-942</t>
+  </si>
+  <si>
+    <t>-219</t>
+  </si>
+  <si>
+    <t>+260</t>
+  </si>
+  <si>
+    <t>+1150</t>
+  </si>
+  <si>
+    <t>+1182</t>
+  </si>
+  <si>
+    <t>+1308</t>
+  </si>
+  <si>
+    <t>+2400</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>64.9%</t>
+  </si>
+  <si>
+    <t>17.1%</t>
+  </si>
+  <si>
+    <t>15.6%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-∞</t>
-  </si>
-  <si>
-    <t>-2603</t>
-  </si>
-  <si>
-    <t>-1289</t>
-  </si>
-  <si>
-    <t>-809</t>
-  </si>
-  <si>
-    <t>-240</t>
-  </si>
-  <si>
-    <t>-176</t>
-  </si>
-  <si>
-    <t>+150</t>
-  </si>
-  <si>
-    <t>+209</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>84.4%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>7.2%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-541</t>
-  </si>
-  <si>
-    <t>+1182</t>
-  </si>
-  <si>
-    <t>+1289</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>-185</t>
+  </si>
+  <si>
+    <t>+485</t>
+  </si>
+  <si>
+    <t>+541</t>
+  </si>
+  <si>
+    <t>+6150</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
   <si>
     <t>+99900</t>
   </si>
   <si>
-    <t>82.2%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-462</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+2757</t>
-  </si>
-  <si>
-    <t>+3604</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>64.7%</t>
+  </si>
+  <si>
+    <t>9.8%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>-183</t>
+  </si>
+  <si>
+    <t>+920</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+1233</t>
+  </si>
+  <si>
+    <t>+1393</t>
+  </si>
+  <si>
+    <t>+4900</t>
   </si>
 </sst>
 </file>
@@ -602,10 +617,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -616,10 +631,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,10 +645,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,10 +659,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,10 +673,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -669,13 +684,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -686,10 +701,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -697,13 +712,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -711,13 +726,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -725,13 +740,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -742,10 +757,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -753,13 +768,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -767,13 +782,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -781,13 +796,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -808,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -822,192 +837,192 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1039,195 +1054,195 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
+++ b/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
   <si>
     <t>Record</t>
   </si>
@@ -39,202 +39,217 @@
     <t>Team Rodriguez</t>
   </si>
   <si>
+    <t xml:space="preserve">Peter Pan + the Lost Boys </t>
+  </si>
+  <si>
     <t>Michael's Monstrous Team</t>
   </si>
   <si>
     <t>Dirty Tone and  The Boys</t>
   </si>
   <si>
-    <t xml:space="preserve">Peter Pan + the Lost Boys </t>
+    <t>The Upside Down</t>
   </si>
   <si>
     <t>Crazy Kat</t>
   </si>
   <si>
+    <t>Toon Squad</t>
+  </si>
+  <si>
+    <t>Wu-Tangs Killabeez</t>
+  </si>
+  <si>
     <t>Febreze Brothers</t>
   </si>
   <si>
+    <t>Crunchwrap Crew</t>
+  </si>
+  <si>
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>The Upside Down</t>
-  </si>
-  <si>
-    <t>Wu-Tangs Killabeez</t>
-  </si>
-  <si>
     <t xml:space="preserve">The Price is Wrong Bob </t>
   </si>
   <si>
-    <t>Toon Squad</t>
-  </si>
-  <si>
-    <t>Crunchwrap Crew</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>98.7%</t>
-  </si>
-  <si>
-    <t>96.7%</t>
-  </si>
-  <si>
-    <t>90.5%</t>
-  </si>
-  <si>
-    <t>90.4%</t>
+    <t>99.1%</t>
+  </si>
+  <si>
+    <t>97.5%</t>
+  </si>
+  <si>
+    <t>95.6%</t>
+  </si>
+  <si>
+    <t>80.1%</t>
   </si>
   <si>
     <t>68.7%</t>
   </si>
   <si>
-    <t>27.8%</t>
+    <t>52.9%</t>
+  </si>
+  <si>
+    <t>27.5%</t>
+  </si>
+  <si>
+    <t>22.9%</t>
+  </si>
+  <si>
+    <t>19.5%</t>
+  </si>
+  <si>
+    <t>19.4%</t>
+  </si>
+  <si>
+    <t>12.0%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-11011</t>
+  </si>
+  <si>
+    <t>-3900</t>
+  </si>
+  <si>
+    <t>-2173</t>
+  </si>
+  <si>
+    <t>-403</t>
+  </si>
+  <si>
+    <t>-219</t>
+  </si>
+  <si>
+    <t>-112</t>
+  </si>
+  <si>
+    <t>+264</t>
+  </si>
+  <si>
+    <t>+337</t>
+  </si>
+  <si>
+    <t>+413</t>
+  </si>
+  <si>
+    <t>+415</t>
+  </si>
+  <si>
+    <t>+733</t>
+  </si>
+  <si>
+    <t>+1983</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>58.2%</t>
+  </si>
+  <si>
+    <t>26.7%</t>
   </si>
   <si>
     <t>8.0%</t>
   </si>
   <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>7.1%</t>
-  </si>
-  <si>
-    <t>4.0%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-7592</t>
-  </si>
-  <si>
-    <t>-2930</t>
-  </si>
-  <si>
-    <t>-953</t>
-  </si>
-  <si>
-    <t>-942</t>
-  </si>
-  <si>
-    <t>-219</t>
-  </si>
-  <si>
-    <t>+260</t>
+    <t>3.9%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-139</t>
+  </si>
+  <si>
+    <t>+275</t>
   </si>
   <si>
     <t>+1150</t>
   </si>
   <si>
-    <t>+1182</t>
-  </si>
-  <si>
-    <t>+1308</t>
-  </si>
-  <si>
-    <t>+2400</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>64.9%</t>
-  </si>
-  <si>
-    <t>17.1%</t>
-  </si>
-  <si>
-    <t>15.6%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
+    <t>+2464</t>
+  </si>
+  <si>
+    <t>+3233</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>42.2%</t>
+  </si>
+  <si>
+    <t>20.8%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>12.2%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-185</t>
-  </si>
-  <si>
-    <t>+485</t>
-  </si>
-  <si>
-    <t>+541</t>
-  </si>
-  <si>
-    <t>+6150</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>64.7%</t>
-  </si>
-  <si>
-    <t>9.8%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>-183</t>
-  </si>
-  <si>
-    <t>+920</t>
-  </si>
-  <si>
-    <t>+987</t>
+    <t>+137</t>
+  </si>
+  <si>
+    <t>+381</t>
+  </si>
+  <si>
+    <t>+700</t>
+  </si>
+  <si>
+    <t>+720</t>
   </si>
   <si>
     <t>+1233</t>
   </si>
   <si>
-    <t>+1393</t>
-  </si>
-  <si>
-    <t>+4900</t>
+    <t>+3126</t>
+  </si>
+  <si>
+    <t>+7043</t>
   </si>
 </sst>
 </file>
@@ -628,7 +643,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -648,7 +663,7 @@
         <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -656,13 +671,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -670,13 +685,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -690,7 +705,7 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -698,13 +713,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -712,13 +727,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -726,13 +741,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -740,13 +755,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -760,7 +775,7 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -768,13 +783,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -782,13 +797,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -802,7 +817,7 @@
         <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -823,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -831,44 +846,44 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -876,13 +891,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -890,139 +905,139 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1057,66 +1072,66 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1124,13 +1139,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1138,41 +1153,41 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1180,55 +1195,55 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1239,10 +1254,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
+++ b/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
   <si>
     <t>Record</t>
   </si>
@@ -30,175 +30,187 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Is it Hockey Season?</t>
+  </si>
+  <si>
     <t>Ertz When I Pee</t>
   </si>
   <si>
-    <t>Is it Hockey Season?</t>
-  </si>
-  <si>
     <t>Team Rodriguez</t>
   </si>
   <si>
+    <t>Dirty Tone and  The Boys</t>
+  </si>
+  <si>
+    <t>The Upside Down</t>
+  </si>
+  <si>
+    <t>Michael's Monstrous Team</t>
+  </si>
+  <si>
+    <t>Toon Squad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
   <si>
-    <t>Michael's Monstrous Team</t>
-  </si>
-  <si>
-    <t>Dirty Tone and  The Boys</t>
-  </si>
-  <si>
-    <t>The Upside Down</t>
+    <t>Wu-Tangs Killabeez</t>
   </si>
   <si>
     <t>Crazy Kat</t>
   </si>
   <si>
-    <t>Toon Squad</t>
-  </si>
-  <si>
-    <t>Wu-Tangs Killabeez</t>
+    <t>Crunchwrap Crew</t>
   </si>
   <si>
     <t>Febreze Brothers</t>
   </si>
   <si>
-    <t>Crunchwrap Crew</t>
+    <t xml:space="preserve">The Price is Wrong Bob </t>
   </si>
   <si>
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t xml:space="preserve">The Price is Wrong Bob </t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.1%</t>
-  </si>
-  <si>
-    <t>97.5%</t>
-  </si>
-  <si>
-    <t>95.6%</t>
-  </si>
-  <si>
-    <t>80.1%</t>
-  </si>
-  <si>
-    <t>68.7%</t>
-  </si>
-  <si>
-    <t>52.9%</t>
-  </si>
-  <si>
-    <t>27.5%</t>
-  </si>
-  <si>
-    <t>22.9%</t>
-  </si>
-  <si>
-    <t>19.5%</t>
-  </si>
-  <si>
-    <t>19.4%</t>
-  </si>
-  <si>
-    <t>12.0%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>91.7%</t>
+  </si>
+  <si>
+    <t>89.3%</t>
+  </si>
+  <si>
+    <t>84.2%</t>
+  </si>
+  <si>
+    <t>83.5%</t>
+  </si>
+  <si>
+    <t>68.3%</t>
+  </si>
+  <si>
+    <t>67.3%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>31.6%</t>
+  </si>
+  <si>
+    <t>30.5%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>0.9%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>-99900</t>
   </si>
   <si>
-    <t>-11011</t>
-  </si>
-  <si>
-    <t>-3900</t>
-  </si>
-  <si>
-    <t>-2173</t>
-  </si>
-  <si>
-    <t>-403</t>
-  </si>
-  <si>
-    <t>-219</t>
-  </si>
-  <si>
-    <t>-112</t>
-  </si>
-  <si>
-    <t>+264</t>
-  </si>
-  <si>
-    <t>+337</t>
-  </si>
-  <si>
-    <t>+413</t>
-  </si>
-  <si>
-    <t>+415</t>
-  </si>
-  <si>
-    <t>+733</t>
-  </si>
-  <si>
-    <t>+1983</t>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-1105</t>
+  </si>
+  <si>
+    <t>-835</t>
+  </si>
+  <si>
+    <t>-533</t>
+  </si>
+  <si>
+    <t>-506</t>
+  </si>
+  <si>
+    <t>-215</t>
+  </si>
+  <si>
+    <t>-206</t>
+  </si>
+  <si>
+    <t>-100</t>
+  </si>
+  <si>
+    <t>+216</t>
+  </si>
+  <si>
+    <t>+228</t>
+  </si>
+  <si>
+    <t>+4248</t>
+  </si>
+  <si>
+    <t>+11011</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>58.2%</t>
-  </si>
-  <si>
-    <t>26.7%</t>
-  </si>
-  <si>
-    <t>8.0%</t>
-  </si>
-  <si>
-    <t>3.9%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
+    <t>63.7%</t>
+  </si>
+  <si>
+    <t>32.0%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
+    <t>0.1%</t>
+  </si>
+  <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-139</t>
-  </si>
-  <si>
-    <t>+275</t>
-  </si>
-  <si>
-    <t>+1150</t>
-  </si>
-  <si>
-    <t>+2464</t>
-  </si>
-  <si>
-    <t>+3233</t>
+    <t>-175</t>
+  </si>
+  <si>
+    <t>+212</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+49900</t>
@@ -207,49 +219,28 @@
     <t>+99900</t>
   </si>
   <si>
-    <t>42.2%</t>
-  </si>
-  <si>
-    <t>20.8%</t>
-  </si>
-  <si>
-    <t>12.5%</t>
-  </si>
-  <si>
-    <t>12.2%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+137</t>
-  </si>
-  <si>
-    <t>+381</t>
-  </si>
-  <si>
-    <t>+700</t>
-  </si>
-  <si>
-    <t>+720</t>
-  </si>
-  <si>
-    <t>+1233</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+7043</t>
+    <t>42.6%</t>
+  </si>
+  <si>
+    <t>38.8%</t>
+  </si>
+  <si>
+    <t>16.8%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>+135</t>
+  </si>
+  <si>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+495</t>
+  </si>
+  <si>
+    <t>+14186</t>
   </si>
 </sst>
 </file>
@@ -632,10 +623,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -646,10 +637,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -657,13 +648,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -671,13 +662,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -685,13 +676,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -702,10 +693,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -713,13 +704,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -730,10 +721,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -741,13 +732,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -755,13 +746,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -772,10 +763,10 @@
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -783,13 +774,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -797,13 +788,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -814,10 +805,10 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -846,30 +837,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -877,13 +868,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -891,13 +882,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -905,55 +896,55 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -964,38 +955,38 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1006,38 +997,38 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1072,7 +1063,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
         <v>71</v>
@@ -1083,10 +1074,10 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
         <v>72</v>
@@ -1094,13 +1085,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
         <v>73</v>
@@ -1108,13 +1099,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
         <v>74</v>
@@ -1125,13 +1116,13 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1139,83 +1130,83 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1226,24 +1217,24 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1251,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
+++ b/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
   <si>
     <t>Record</t>
   </si>
@@ -30,36 +30,36 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Ertz When I Pee</t>
+  </si>
+  <si>
     <t>Is it Hockey Season?</t>
   </si>
   <si>
-    <t>Ertz When I Pee</t>
-  </si>
-  <si>
     <t>Team Rodriguez</t>
   </si>
   <si>
+    <t>The Upside Down</t>
+  </si>
+  <si>
+    <t>Toon Squad</t>
+  </si>
+  <si>
+    <t>Crazy Kat</t>
+  </si>
+  <si>
     <t>Dirty Tone and  The Boys</t>
   </si>
   <si>
-    <t>The Upside Down</t>
-  </si>
-  <si>
     <t>Michael's Monstrous Team</t>
   </si>
   <si>
-    <t>Toon Squad</t>
+    <t>Wu-Tangs Killabeez</t>
   </si>
   <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
   <si>
-    <t>Wu-Tangs Killabeez</t>
-  </si>
-  <si>
-    <t>Crazy Kat</t>
-  </si>
-  <si>
     <t>Crunchwrap Crew</t>
   </si>
   <si>
@@ -72,175 +72,160 @@
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>1-5</t>
   </si>
   <si>
     <t>100.0%</t>
   </si>
   <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>91.7%</t>
-  </si>
-  <si>
-    <t>89.3%</t>
-  </si>
-  <si>
-    <t>84.2%</t>
-  </si>
-  <si>
-    <t>83.5%</t>
-  </si>
-  <si>
-    <t>68.3%</t>
-  </si>
-  <si>
-    <t>67.3%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>31.6%</t>
-  </si>
-  <si>
-    <t>30.5%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
+    <t>99.9%</t>
+  </si>
+  <si>
+    <t>88.6%</t>
+  </si>
+  <si>
+    <t>87.0%</t>
+  </si>
+  <si>
+    <t>83.4%</t>
+  </si>
+  <si>
+    <t>78.9%</t>
+  </si>
+  <si>
+    <t>67.1%</t>
+  </si>
+  <si>
+    <t>63.9%</t>
+  </si>
+  <si>
+    <t>58.1%</t>
+  </si>
+  <si>
+    <t>55.5%</t>
+  </si>
+  <si>
+    <t>11.9%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-777</t>
+  </si>
+  <si>
+    <t>-669</t>
+  </si>
+  <si>
+    <t>-502</t>
+  </si>
+  <si>
+    <t>-374</t>
+  </si>
+  <si>
+    <t>-204</t>
+  </si>
+  <si>
+    <t>-177</t>
+  </si>
+  <si>
+    <t>-139</t>
+  </si>
+  <si>
+    <t>-125</t>
+  </si>
+  <si>
+    <t>+740</t>
+  </si>
+  <si>
+    <t>+2603</t>
+  </si>
+  <si>
+    <t>+4900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>51.3%</t>
+  </si>
+  <si>
+    <t>46.5%</t>
   </si>
   <si>
     <t>0.9%</t>
   </si>
   <si>
-    <t>0.6%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-49900</t>
-  </si>
-  <si>
-    <t>-1105</t>
-  </si>
-  <si>
-    <t>-835</t>
-  </si>
-  <si>
-    <t>-533</t>
-  </si>
-  <si>
-    <t>-506</t>
-  </si>
-  <si>
-    <t>-215</t>
-  </si>
-  <si>
-    <t>-206</t>
-  </si>
-  <si>
-    <t>-100</t>
-  </si>
-  <si>
-    <t>+216</t>
-  </si>
-  <si>
-    <t>+228</t>
-  </si>
-  <si>
-    <t>+4248</t>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-105</t>
+  </si>
+  <si>
+    <t>+115</t>
   </si>
   <si>
     <t>+11011</t>
   </si>
   <si>
-    <t>+16567</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>63.7%</t>
-  </si>
-  <si>
-    <t>32.0%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-175</t>
-  </si>
-  <si>
-    <t>+212</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>42.6%</t>
-  </si>
-  <si>
-    <t>38.8%</t>
-  </si>
-  <si>
-    <t>16.8%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>+135</t>
-  </si>
-  <si>
-    <t>+158</t>
-  </si>
-  <si>
-    <t>+495</t>
-  </si>
-  <si>
     <t>+14186</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>69.9%</t>
+  </si>
+  <si>
+    <t>15.5%</t>
+  </si>
+  <si>
+    <t>12.1%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>-232</t>
+  </si>
+  <si>
+    <t>+545</t>
+  </si>
+  <si>
+    <t>+726</t>
+  </si>
+  <si>
+    <t>+4067</t>
   </si>
 </sst>
 </file>
@@ -640,7 +625,7 @@
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -654,7 +639,7 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -668,7 +653,7 @@
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -676,13 +661,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -696,7 +681,7 @@
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -704,13 +689,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -724,7 +709,7 @@
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -732,13 +717,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -746,13 +731,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -760,13 +745,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -774,13 +759,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -794,7 +779,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -802,13 +787,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
         <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -837,72 +822,72 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -910,18 +895,18 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -930,35 +915,35 @@
         <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -969,52 +954,52 @@
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1022,13 +1007,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1049,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1060,13 +1045,13 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1077,10 +1062,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1088,13 +1073,13 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1102,55 +1087,55 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1161,10 +1146,10 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1175,24 +1160,24 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1203,38 +1188,38 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1245,10 +1230,10 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
+++ b/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
   <si>
     <t>Record</t>
   </si>
@@ -36,196 +36,208 @@
     <t>Is it Hockey Season?</t>
   </si>
   <si>
+    <t>Toon Squad</t>
+  </si>
+  <si>
+    <t>Dirty Tone and  The Boys</t>
+  </si>
+  <si>
+    <t>Crazy Kat</t>
+  </si>
+  <si>
+    <t>The Upside Down</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Pan + the Lost Boys </t>
+  </si>
+  <si>
+    <t>Wu-Tangs Killabeez</t>
+  </si>
+  <si>
+    <t>Michael's Monstrous Team</t>
+  </si>
+  <si>
     <t>Team Rodriguez</t>
   </si>
   <si>
-    <t>The Upside Down</t>
-  </si>
-  <si>
-    <t>Toon Squad</t>
-  </si>
-  <si>
-    <t>Crazy Kat</t>
-  </si>
-  <si>
-    <t>Dirty Tone and  The Boys</t>
-  </si>
-  <si>
-    <t>Michael's Monstrous Team</t>
-  </si>
-  <si>
-    <t>Wu-Tangs Killabeez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Pan + the Lost Boys </t>
-  </si>
-  <si>
     <t>Crunchwrap Crew</t>
   </si>
   <si>
+    <t xml:space="preserve">The Price is Wrong Bob </t>
+  </si>
+  <si>
     <t>Febreze Brothers</t>
   </si>
   <si>
-    <t xml:space="preserve">The Price is Wrong Bob </t>
-  </si>
-  <si>
     <t>the   jadey bunch</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>1-5</t>
-  </si>
-  <si>
-    <t>100.0%</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>6-1</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>1-6</t>
   </si>
   <si>
     <t>99.9%</t>
   </si>
   <si>
-    <t>88.6%</t>
-  </si>
-  <si>
-    <t>87.0%</t>
-  </si>
-  <si>
-    <t>83.4%</t>
-  </si>
-  <si>
-    <t>78.9%</t>
-  </si>
-  <si>
-    <t>67.1%</t>
-  </si>
-  <si>
-    <t>63.9%</t>
-  </si>
-  <si>
-    <t>58.1%</t>
-  </si>
-  <si>
-    <t>55.5%</t>
-  </si>
-  <si>
-    <t>11.9%</t>
-  </si>
-  <si>
-    <t>3.7%</t>
+    <t>99.2%</t>
+  </si>
+  <si>
+    <t>91.3%</t>
+  </si>
+  <si>
+    <t>83.6%</t>
+  </si>
+  <si>
+    <t>79.7%</t>
+  </si>
+  <si>
+    <t>79.6%</t>
+  </si>
+  <si>
+    <t>76.3%</t>
+  </si>
+  <si>
+    <t>68.9%</t>
+  </si>
+  <si>
+    <t>68.1%</t>
+  </si>
+  <si>
+    <t>49.5%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-99900</t>
+  </si>
+  <si>
+    <t>-12400</t>
+  </si>
+  <si>
+    <t>-1049</t>
+  </si>
+  <si>
+    <t>-510</t>
+  </si>
+  <si>
+    <t>-393</t>
+  </si>
+  <si>
+    <t>-390</t>
+  </si>
+  <si>
+    <t>-322</t>
+  </si>
+  <si>
+    <t>-222</t>
+  </si>
+  <si>
+    <t>-213</t>
+  </si>
+  <si>
+    <t>+102</t>
+  </si>
+  <si>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>53.8%</t>
+  </si>
+  <si>
+    <t>30.3%</t>
+  </si>
+  <si>
+    <t>7.4%</t>
   </si>
   <si>
     <t>2.0%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-777</t>
-  </si>
-  <si>
-    <t>-669</t>
-  </si>
-  <si>
-    <t>-502</t>
-  </si>
-  <si>
-    <t>-374</t>
-  </si>
-  <si>
-    <t>-204</t>
-  </si>
-  <si>
-    <t>-177</t>
-  </si>
-  <si>
-    <t>-139</t>
-  </si>
-  <si>
-    <t>-125</t>
-  </si>
-  <si>
-    <t>+740</t>
-  </si>
-  <si>
-    <t>+2603</t>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>1.5%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>-116</t>
+  </si>
+  <si>
+    <t>+230</t>
+  </si>
+  <si>
+    <t>+1251</t>
   </si>
   <si>
     <t>+4900</t>
   </si>
   <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>51.3%</t>
-  </si>
-  <si>
-    <t>46.5%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-105</t>
-  </si>
-  <si>
-    <t>+115</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>69.9%</t>
-  </si>
-  <si>
-    <t>15.5%</t>
-  </si>
-  <si>
-    <t>12.1%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>-232</t>
-  </si>
-  <si>
-    <t>+545</t>
-  </si>
-  <si>
-    <t>+726</t>
-  </si>
-  <si>
-    <t>+4067</t>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>+6567</t>
+  </si>
+  <si>
+    <t>+8991</t>
+  </si>
+  <si>
+    <t>72.2%</t>
+  </si>
+  <si>
+    <t>15.6%</t>
+  </si>
+  <si>
+    <t>9.6%</t>
+  </si>
+  <si>
+    <t>2.5%</t>
+  </si>
+  <si>
+    <t>-260</t>
+  </si>
+  <si>
+    <t>+541</t>
+  </si>
+  <si>
+    <t>+942</t>
+  </si>
+  <si>
+    <t>+3900</t>
   </si>
 </sst>
 </file>
@@ -608,10 +620,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -622,10 +634,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -636,10 +648,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -647,13 +659,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -661,13 +673,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,13 +687,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -689,13 +701,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -703,13 +715,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -720,10 +732,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -731,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -745,13 +757,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -759,13 +771,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -773,13 +785,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -787,13 +799,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -814,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -822,125 +834,125 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>49</v>
@@ -948,58 +960,58 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1007,13 +1019,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1045,13 +1057,13 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1059,13 +1071,13 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1073,13 +1085,13 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1087,153 +1099,153 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
+++ b/data/odds/THE BEST OF THE BEST 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
   <si>
     <t>Record</t>
   </si>
@@ -42,12 +42,12 @@
     <t>Dirty Tone and  The Boys</t>
   </si>
   <si>
+    <t>The Upside Down</t>
+  </si>
+  <si>
     <t>Crazy Kat</t>
   </si>
   <si>
-    <t>The Upside Down</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peter Pan + the Lost Boys </t>
   </si>
   <si>
@@ -90,154 +90,160 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>99.9%</t>
-  </si>
-  <si>
-    <t>99.2%</t>
-  </si>
-  <si>
-    <t>91.3%</t>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>99.1%</t>
+  </si>
+  <si>
+    <t>92.0%</t>
   </si>
   <si>
     <t>83.6%</t>
   </si>
   <si>
-    <t>79.7%</t>
-  </si>
-  <si>
-    <t>79.6%</t>
-  </si>
-  <si>
-    <t>76.3%</t>
-  </si>
-  <si>
-    <t>68.9%</t>
-  </si>
-  <si>
-    <t>68.1%</t>
-  </si>
-  <si>
-    <t>49.5%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
+    <t>79.0%</t>
+  </si>
+  <si>
+    <t>77.3%</t>
+  </si>
+  <si>
+    <t>74.9%</t>
+  </si>
+  <si>
+    <t>69.5%</t>
+  </si>
+  <si>
+    <t>68.4%</t>
+  </si>
+  <si>
+    <t>51.9%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
+    <t>-49900</t>
+  </si>
+  <si>
+    <t>-11011</t>
+  </si>
+  <si>
+    <t>-1150</t>
+  </si>
+  <si>
+    <t>-510</t>
+  </si>
+  <si>
+    <t>-376</t>
+  </si>
+  <si>
+    <t>-341</t>
+  </si>
+  <si>
+    <t>-298</t>
+  </si>
+  <si>
+    <t>-228</t>
+  </si>
+  <si>
+    <t>-216</t>
+  </si>
+  <si>
+    <t>-108</t>
+  </si>
+  <si>
+    <t>+2603</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>55.1%</t>
+  </si>
+  <si>
+    <t>28.8%</t>
+  </si>
+  <si>
+    <t>7.2%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>1.1%</t>
+  </si>
+  <si>
+    <t>0.8%</t>
+  </si>
+  <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-99900</t>
-  </si>
-  <si>
-    <t>-12400</t>
-  </si>
-  <si>
-    <t>-1049</t>
-  </si>
-  <si>
-    <t>-510</t>
-  </si>
-  <si>
-    <t>-393</t>
-  </si>
-  <si>
-    <t>-390</t>
-  </si>
-  <si>
-    <t>-322</t>
-  </si>
-  <si>
-    <t>-222</t>
-  </si>
-  <si>
-    <t>-213</t>
-  </si>
-  <si>
-    <t>+102</t>
-  </si>
-  <si>
-    <t>+3471</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>53.8%</t>
-  </si>
-  <si>
-    <t>30.3%</t>
-  </si>
-  <si>
-    <t>7.4%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>-116</t>
-  </si>
-  <si>
-    <t>+230</t>
-  </si>
-  <si>
-    <t>+1251</t>
-  </si>
-  <si>
-    <t>+4900</t>
+    <t>-123</t>
+  </si>
+  <si>
+    <t>+247</t>
+  </si>
+  <si>
+    <t>+1289</t>
+  </si>
+  <si>
+    <t>+4067</t>
   </si>
   <si>
     <t>+5782</t>
   </si>
   <si>
-    <t>+6567</t>
+    <t>+8233</t>
   </si>
   <si>
     <t>+8991</t>
   </si>
   <si>
+    <t>+12400</t>
+  </si>
+  <si>
     <t>72.2%</t>
   </si>
   <si>
-    <t>15.6%</t>
-  </si>
-  <si>
-    <t>9.6%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
+    <t>14.8%</t>
+  </si>
+  <si>
+    <t>9.9%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
   </si>
   <si>
     <t>-260</t>
   </si>
   <si>
-    <t>+541</t>
-  </si>
-  <si>
-    <t>+942</t>
-  </si>
-  <si>
-    <t>+3900</t>
+    <t>+576</t>
+  </si>
+  <si>
+    <t>+910</t>
+  </si>
+  <si>
+    <t>+3233</t>
   </si>
 </sst>
 </file>
@@ -623,7 +629,7 @@
         <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -637,7 +643,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -651,7 +657,7 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -665,7 +671,7 @@
         <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -679,7 +685,7 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -693,7 +699,7 @@
         <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -707,7 +713,7 @@
         <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -721,7 +727,7 @@
         <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -735,7 +741,7 @@
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -749,7 +755,7 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -763,7 +769,7 @@
         <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -777,7 +783,7 @@
         <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -791,7 +797,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -802,10 +808,10 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -840,10 +846,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -854,10 +860,10 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -868,10 +874,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -882,24 +888,24 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -910,7 +916,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
@@ -918,13 +924,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
@@ -932,86 +938,86 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1022,10 +1028,10 @@
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1060,10 +1066,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1074,10 +1080,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1088,10 +1094,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1102,136 +1108,136 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1242,10 +1248,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
